--- a/research/traditional_assets/database/data/germany/germany_steel.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_steel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.02</v>
-      </c>
-      <c r="E2">
-        <v>0.018285</v>
-      </c>
-      <c r="F2">
-        <v>-0.2835</v>
+        <v>0.00584</v>
       </c>
       <c r="G2">
-        <v>0.01676914932542611</v>
+        <v>0.03379040532622352</v>
       </c>
       <c r="H2">
-        <v>0.0006436995694347855</v>
+        <v>0.01412667180115705</v>
       </c>
       <c r="I2">
-        <v>-0.03538915985490915</v>
+        <v>-0.003966010014814967</v>
       </c>
       <c r="J2">
-        <v>-0.03462477279723311</v>
+        <v>-0.003966010014814967</v>
       </c>
       <c r="K2">
-        <v>-1834.3</v>
+        <v>-1679.7</v>
       </c>
       <c r="L2">
-        <v>-0.03556440121127197</v>
+        <v>-0.04297875497990129</v>
       </c>
       <c r="M2">
-        <v>163.27</v>
+        <v>103.7</v>
       </c>
       <c r="N2">
-        <v>0.02629612330686595</v>
+        <v>0.04103517866328994</v>
       </c>
       <c r="O2">
-        <v>-0.08900943139072126</v>
+        <v>-0.06173721497886527</v>
       </c>
       <c r="P2">
-        <v>163.27</v>
+        <v>103.7</v>
       </c>
       <c r="Q2">
-        <v>0.02629612330686595</v>
+        <v>0.04103517866328994</v>
       </c>
       <c r="R2">
-        <v>-0.08900943139072126</v>
+        <v>-0.06173721497886527</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8981.800999999999</v>
+        <v>6543.6</v>
       </c>
       <c r="V2">
-        <v>1.446601008230121</v>
+        <v>2.589371216018361</v>
       </c>
       <c r="W2">
-        <v>0.07011736382786639</v>
+        <v>-0.1340585493551271</v>
       </c>
       <c r="X2">
-        <v>0.1072515916579123</v>
+        <v>0.1076838265136746</v>
       </c>
       <c r="Y2">
-        <v>-0.03713422783004595</v>
+        <v>-0.2417423758688017</v>
       </c>
       <c r="Z2">
-        <v>3.434831027986604</v>
+        <v>6.019761871755772</v>
       </c>
       <c r="AA2">
-        <v>-0.007720421668644024</v>
+        <v>-0.02387443587018468</v>
       </c>
       <c r="AB2">
-        <v>0.07982335905338776</v>
+        <v>0.08293638392870677</v>
       </c>
       <c r="AC2">
-        <v>-0.09167286294318626</v>
+        <v>-0.1068108197988915</v>
       </c>
       <c r="AD2">
-        <v>4994.7</v>
+        <v>1642.9</v>
       </c>
       <c r="AE2">
-        <v>9.493008988151118</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>5004.193008988151</v>
+        <v>1642.9</v>
       </c>
       <c r="AG2">
-        <v>-3977.607991011849</v>
+        <v>-4900.700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4462812361385844</v>
+        <v>0.3939808153477218</v>
       </c>
       <c r="AI2">
-        <v>0.2097763761548899</v>
+        <v>0.1245055094957334</v>
       </c>
       <c r="AJ2">
-        <v>-1.782647889648302</v>
+        <v>2.064669700033704</v>
       </c>
       <c r="AK2">
-        <v>-0.267436521512009</v>
+        <v>-0.7367479479238704</v>
       </c>
       <c r="AL2">
-        <v>152.147</v>
+        <v>72.5</v>
       </c>
       <c r="AM2">
-        <v>-71.41299999999998</v>
+        <v>-163.9</v>
       </c>
       <c r="AN2">
-        <v>-7.114450537710988</v>
+        <v>2.975729034595182</v>
       </c>
       <c r="AO2">
-        <v>-12.02989871637298</v>
+        <v>-2.137931034482758</v>
       </c>
       <c r="AP2">
-        <v>5.665704709083182</v>
+        <v>-8.876471653685927</v>
       </c>
       <c r="AQ2">
-        <v>25.62996933331467</v>
+        <v>0.9456985967053081</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salzgitter AG (XTRA:SZG)</t>
+          <t>thyssenkrupp AG (XTRA:TKA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,49 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0421</v>
-      </c>
-      <c r="E3">
-        <v>0.0399</v>
-      </c>
-      <c r="F3">
-        <v>-0.368</v>
+        <v>0.00584</v>
       </c>
       <c r="G3">
-        <v>0.09354558268693501</v>
+        <v>0.03379040532622352</v>
       </c>
       <c r="H3">
-        <v>0.08570439832203718</v>
+        <v>0.01412667180115705</v>
       </c>
       <c r="I3">
-        <v>-0.00257000108017845</v>
+        <v>-0.003966010014814967</v>
       </c>
       <c r="J3">
-        <v>-0.002417212426251552</v>
+        <v>-0.003966010014814967</v>
       </c>
       <c r="K3">
-        <v>349.5</v>
+        <v>-1679.7</v>
       </c>
       <c r="L3">
-        <v>0.02949939650733898</v>
+        <v>-0.04297875497990129</v>
       </c>
       <c r="M3">
-        <v>57.3</v>
+        <v>103.7</v>
       </c>
       <c r="N3">
-        <v>0.03422939068100359</v>
+        <v>0.04103517866328994</v>
       </c>
       <c r="O3">
-        <v>0.1639484978540773</v>
+        <v>-0.06173721497886527</v>
       </c>
       <c r="P3">
-        <v>57.3</v>
+        <v>103.7</v>
       </c>
       <c r="Q3">
-        <v>0.03422939068100359</v>
+        <v>0.04103517866328994</v>
       </c>
       <c r="R3">
-        <v>0.1639484978540773</v>
+        <v>-0.06173721497886527</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,335 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1214</v>
+        <v>6543.6</v>
       </c>
       <c r="V3">
-        <v>0.7252090800477897</v>
+        <v>2.589371216018361</v>
       </c>
       <c r="W3">
-        <v>0.07011736382786639</v>
+        <v>-0.1340585493551271</v>
       </c>
       <c r="X3">
-        <v>0.1179852201367151</v>
+        <v>0.1076838265136746</v>
       </c>
       <c r="Y3">
-        <v>-0.04786785630884868</v>
+        <v>-0.2417423758688017</v>
       </c>
       <c r="Z3">
-        <v>1.995337243280447</v>
+        <v>6.019761871755772</v>
       </c>
       <c r="AA3">
-        <v>-0.004823153979020014</v>
+        <v>-0.02387443587018468</v>
       </c>
       <c r="AB3">
-        <v>0.07526933182744611</v>
+        <v>0.08293638392870677</v>
       </c>
       <c r="AC3">
-        <v>-0.08009248580646612</v>
+        <v>-0.1068108197988915</v>
       </c>
       <c r="AD3">
-        <v>1793</v>
+        <v>1642.9</v>
       </c>
       <c r="AE3">
-        <v>9.493008988151118</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1802.493008988151</v>
+        <v>1642.9</v>
       </c>
       <c r="AG3">
-        <v>588.4930089881511</v>
+        <v>-4900.700000000001</v>
       </c>
       <c r="AH3">
-        <v>0.5184802628188731</v>
+        <v>0.3939808153477218</v>
       </c>
       <c r="AI3">
-        <v>0.2532483005900978</v>
+        <v>0.1245055094957334</v>
       </c>
       <c r="AJ3">
-        <v>0.2601082110089442</v>
+        <v>2.064669700033704</v>
       </c>
       <c r="AK3">
-        <v>0.09968556041180404</v>
+        <v>-0.7367479479238704</v>
       </c>
       <c r="AL3">
-        <v>53.7</v>
+        <v>72.5</v>
       </c>
       <c r="AM3">
-        <v>16.40000000000001</v>
+        <v>-163.9</v>
       </c>
       <c r="AN3">
-        <v>6.400142780653222</v>
+        <v>2.975729034595182</v>
       </c>
       <c r="AO3">
-        <v>-0.6610800744878956</v>
+        <v>-2.137931034482758</v>
       </c>
       <c r="AP3">
-        <v>2.100635405990188</v>
+        <v>-8.876471653685927</v>
       </c>
       <c r="AQ3">
-        <v>-2.164634146341462</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eisen- und Hüttenwerke AG (DB:EIS)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Steel</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.133</v>
-      </c>
-      <c r="E4">
-        <v>-0.00333</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>-5.211538461538461</v>
-      </c>
-      <c r="J4">
-        <v>-5.183669271904565</v>
-      </c>
-      <c r="K4">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L4">
-        <v>59.61538461538462</v>
-      </c>
-      <c r="M4">
-        <v>7.57</v>
-      </c>
-      <c r="N4">
-        <v>0.03950939457202506</v>
-      </c>
-      <c r="O4">
-        <v>0.8139784946236559</v>
-      </c>
-      <c r="P4">
-        <v>7.57</v>
-      </c>
-      <c r="Q4">
-        <v>0.03950939457202506</v>
-      </c>
-      <c r="R4">
-        <v>0.8139784946236559</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.001</v>
-      </c>
-      <c r="V4">
-        <v>5.219206680584551e-06</v>
-      </c>
-      <c r="W4">
-        <v>0.08959537572254336</v>
-      </c>
-      <c r="X4">
-        <v>0.08395244127454224</v>
-      </c>
-      <c r="Y4">
-        <v>0.005642934448001125</v>
-      </c>
-      <c r="Z4">
-        <v>0.001489373890130034</v>
-      </c>
-      <c r="AA4">
-        <v>-0.007720421668644024</v>
-      </c>
-      <c r="AB4">
-        <v>0.08395244127454224</v>
-      </c>
-      <c r="AC4">
-        <v>-0.09167286294318626</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-0.001</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-5.219233920845098e-06</v>
-      </c>
-      <c r="AK4">
-        <v>-9.784831554124797e-06</v>
-      </c>
-      <c r="AL4">
-        <v>0.047</v>
-      </c>
-      <c r="AM4">
-        <v>-9.413</v>
-      </c>
-      <c r="AO4">
-        <v>-17.29787234042553</v>
-      </c>
-      <c r="AQ4">
-        <v>0.08636991394879422</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>thyssenkrupp AG (XTRA:TKA)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Steel</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.02</v>
-      </c>
-      <c r="F5">
-        <v>-0.199</v>
-      </c>
-      <c r="G5">
-        <v>-0.006126507085504294</v>
-      </c>
-      <c r="H5">
-        <v>-0.02472249490296761</v>
-      </c>
-      <c r="I5">
-        <v>-0.04515593143547535</v>
-      </c>
-      <c r="J5">
-        <v>-0.04515593143547535</v>
-      </c>
-      <c r="K5">
-        <v>-2193.1</v>
-      </c>
-      <c r="L5">
-        <v>-0.05520149009539631</v>
-      </c>
-      <c r="M5">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="N5">
-        <v>0.02265558446342643</v>
-      </c>
-      <c r="O5">
-        <v>-0.04486799507546396</v>
-      </c>
-      <c r="P5">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="Q5">
-        <v>0.02265558446342643</v>
-      </c>
-      <c r="R5">
-        <v>-0.04486799507546396</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>7767.8</v>
-      </c>
-      <c r="V5">
-        <v>1.788455782469551</v>
-      </c>
-      <c r="W5">
-        <v>-0.1574790145264715</v>
-      </c>
-      <c r="X5">
-        <v>0.1072515916579123</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2647306061843838</v>
-      </c>
-      <c r="Z5">
-        <v>4.427418815610583</v>
-      </c>
-      <c r="AA5">
-        <v>-0.1999242204738449</v>
-      </c>
-      <c r="AB5">
-        <v>0.07982335905338776</v>
-      </c>
-      <c r="AC5">
-        <v>-0.2797475795272327</v>
-      </c>
-      <c r="AD5">
-        <v>3201.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>3201.7</v>
-      </c>
-      <c r="AG5">
-        <v>-4566.1</v>
-      </c>
-      <c r="AH5">
-        <v>0.4243472498343274</v>
-      </c>
-      <c r="AI5">
-        <v>0.1924653746272963</v>
-      </c>
-      <c r="AJ5">
-        <v>20.49416517055654</v>
-      </c>
-      <c r="AK5">
-        <v>-0.5149310959243973</v>
-      </c>
-      <c r="AL5">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="AM5">
-        <v>-78.40000000000001</v>
-      </c>
-      <c r="AN5">
-        <v>-3.259723070657707</v>
-      </c>
-      <c r="AO5">
-        <v>-18.23170731707317</v>
-      </c>
-      <c r="AP5">
-        <v>4.648849521482386</v>
-      </c>
-      <c r="AQ5">
-        <v>22.88265306122449</v>
+        <v>0.9456985967053081</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_steel.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_steel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,41 +590,47 @@
       <c r="D2">
         <v>0.00584</v>
       </c>
+      <c r="E2">
+        <v>0.0165</v>
+      </c>
+      <c r="F2">
+        <v>0.078</v>
+      </c>
       <c r="G2">
-        <v>0.03379040532622352</v>
+        <v>0.03542256434624281</v>
       </c>
       <c r="H2">
-        <v>0.01412667180115705</v>
+        <v>0.01824245185542534</v>
       </c>
       <c r="I2">
-        <v>-0.003966010014814967</v>
+        <v>-0.008503227744085044</v>
       </c>
       <c r="J2">
-        <v>-0.003966010014814967</v>
+        <v>-0.008424988678891535</v>
       </c>
       <c r="K2">
-        <v>-1679.7</v>
+        <v>-1882.2</v>
       </c>
       <c r="L2">
-        <v>-0.04297875497990129</v>
+        <v>-0.03737448882364382</v>
       </c>
       <c r="M2">
-        <v>103.7</v>
+        <v>140.8</v>
       </c>
       <c r="N2">
-        <v>0.04103517866328994</v>
+        <v>0.03881675075124749</v>
       </c>
       <c r="O2">
-        <v>-0.06173721497886527</v>
+        <v>-0.074806077993837</v>
       </c>
       <c r="P2">
-        <v>103.7</v>
+        <v>140.8</v>
       </c>
       <c r="Q2">
-        <v>0.04103517866328994</v>
+        <v>0.03881675075124749</v>
       </c>
       <c r="R2">
-        <v>-0.06173721497886527</v>
+        <v>-0.074806077993837</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6543.6</v>
+        <v>7192.3</v>
       </c>
       <c r="V2">
-        <v>2.589371216018361</v>
+        <v>1.982824690541174</v>
       </c>
       <c r="W2">
-        <v>-0.1340585493551271</v>
+        <v>-0.04040575447329223</v>
       </c>
       <c r="X2">
-        <v>0.1076838265136746</v>
+        <v>0.1076440407153502</v>
       </c>
       <c r="Y2">
-        <v>-0.2417423758688017</v>
+        <v>-0.1480497951886424</v>
       </c>
       <c r="Z2">
-        <v>6.019761871755772</v>
+        <v>4.023271254447228</v>
       </c>
       <c r="AA2">
         <v>-0.02387443587018468</v>
       </c>
       <c r="AB2">
-        <v>0.08293638392870677</v>
+        <v>0.08291227297164545</v>
       </c>
       <c r="AC2">
-        <v>-0.1068108197988915</v>
+        <v>-0.1067867088418301</v>
       </c>
       <c r="AD2">
-        <v>1642.9</v>
+        <v>3462.1</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>40.11634241760427</v>
       </c>
       <c r="AF2">
-        <v>1642.9</v>
+        <v>3502.216342417604</v>
       </c>
       <c r="AG2">
-        <v>-4900.700000000001</v>
+        <v>-3690.083657582396</v>
       </c>
       <c r="AH2">
-        <v>0.3939808153477218</v>
+        <v>0.4912277599506855</v>
       </c>
       <c r="AI2">
-        <v>0.1245055094957334</v>
+        <v>0.1730522195645776</v>
       </c>
       <c r="AJ2">
-        <v>2.064669700033704</v>
+        <v>58.7745887970861</v>
       </c>
       <c r="AK2">
-        <v>-0.7367479479238704</v>
+        <v>-0.2828600474462943</v>
       </c>
       <c r="AL2">
-        <v>72.5</v>
+        <v>180.027</v>
       </c>
       <c r="AM2">
-        <v>-163.9</v>
+        <v>-112.773</v>
       </c>
       <c r="AN2">
-        <v>2.975729034595182</v>
+        <v>4.693736442516269</v>
       </c>
       <c r="AO2">
-        <v>-2.137931034482758</v>
+        <v>-2.400773217350731</v>
       </c>
       <c r="AP2">
-        <v>-8.876471653685927</v>
+        <v>-5.002824915377435</v>
       </c>
       <c r="AQ2">
-        <v>0.9456985967053081</v>
+        <v>3.832513101540261</v>
       </c>
     </row>
     <row r="3">
@@ -710,127 +716,389 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Eisen- und Hüttenwerke AG (DB:EIS)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.14</v>
+      </c>
+      <c r="E3">
+        <v>0.0165</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>-5.187096774193549</v>
+      </c>
+      <c r="J3">
+        <v>-5.043915755798454</v>
+      </c>
+      <c r="K3">
+        <v>11.8</v>
+      </c>
+      <c r="L3">
+        <v>76.12903225806453</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>0.04690431519699813</v>
+      </c>
+      <c r="O3">
+        <v>0.847457627118644</v>
+      </c>
+      <c r="P3">
+        <v>10</v>
+      </c>
+      <c r="Q3">
+        <v>0.04690431519699813</v>
+      </c>
+      <c r="R3">
+        <v>0.847457627118644</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.1154598825831703</v>
+      </c>
+      <c r="X3">
+        <v>0.08830218928668868</v>
+      </c>
+      <c r="Y3">
+        <v>0.02715769329648159</v>
+      </c>
+      <c r="Z3">
+        <v>0.001516648890889343</v>
+      </c>
+      <c r="AA3">
+        <v>-0.00764984923677101</v>
+      </c>
+      <c r="AB3">
+        <v>0.08830218928668868</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09595203852345968</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0.027</v>
+      </c>
+      <c r="AM3">
+        <v>-10.073</v>
+      </c>
+      <c r="AO3">
+        <v>-29.77777777777778</v>
+      </c>
+      <c r="AQ3">
+        <v>0.07981733346570039</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>thyssenkrupp AG (XTRA:TKA)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.00584</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>0.03379040532622352</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>0.01412667180115705</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>-0.003966010014814967</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>-0.003966010014814967</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <v>-1679.7</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>-0.04297875497990129</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>103.7</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.04103517866328994</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>-0.06173721497886527</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>103.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.04103517866328994</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>-0.06173721497886527</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>6543.6</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>2.589371216018361</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>-0.1340585493551271</v>
       </c>
-      <c r="X3">
-        <v>0.1076838265136746</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2417423758688017</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.1076440407153502</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2417025900704773</v>
+      </c>
+      <c r="Z4">
         <v>6.019761871755772</v>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <v>-0.02387443587018468</v>
       </c>
-      <c r="AB3">
-        <v>0.08293638392870677</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1068108197988915</v>
-      </c>
-      <c r="AD3">
+      <c r="AB4">
+        <v>0.08291227297164545</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1067867088418301</v>
+      </c>
+      <c r="AD4">
         <v>1642.9</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>1642.9</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>-4900.700000000001</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.3939808153477218</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.1245055094957334</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>2.064669700033704</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>-0.7367479479238704</v>
       </c>
-      <c r="AL3">
+      <c r="AL4">
         <v>72.5</v>
       </c>
-      <c r="AM3">
+      <c r="AM4">
         <v>-163.9</v>
       </c>
-      <c r="AN3">
+      <c r="AN4">
         <v>2.975729034595182</v>
       </c>
-      <c r="AO3">
+      <c r="AO4">
         <v>-2.137931034482758</v>
       </c>
-      <c r="AP3">
+      <c r="AP4">
         <v>-8.876471653685927</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ4">
         <v>0.9456985967053081</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Salzgitter AG (XTRA:SZG)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0239</v>
+      </c>
+      <c r="F5">
+        <v>0.078</v>
+      </c>
+      <c r="G5">
+        <v>0.04107888600232305</v>
+      </c>
+      <c r="H5">
+        <v>0.0325048987879379</v>
+      </c>
+      <c r="I5">
+        <v>-0.02415463930588128</v>
+      </c>
+      <c r="J5">
+        <v>-0.02415463930588128</v>
+      </c>
+      <c r="K5">
+        <v>-214.3</v>
+      </c>
+      <c r="L5">
+        <v>-0.01900109058989387</v>
+      </c>
+      <c r="M5">
+        <v>27.1</v>
+      </c>
+      <c r="N5">
+        <v>0.03055242390078918</v>
+      </c>
+      <c r="O5">
+        <v>-0.1264582361175922</v>
+      </c>
+      <c r="P5">
+        <v>27.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.03055242390078918</v>
+      </c>
+      <c r="R5">
+        <v>-0.1264582361175922</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>648.7</v>
+      </c>
+      <c r="V5">
+        <v>0.7313416009019166</v>
+      </c>
+      <c r="W5">
+        <v>-0.04040575447329223</v>
+      </c>
+      <c r="X5">
+        <v>0.1506669137404504</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1910726682137427</v>
+      </c>
+      <c r="Z5">
+        <v>1.904212345607929</v>
+      </c>
+      <c r="AA5">
+        <v>-0.04599556236996567</v>
+      </c>
+      <c r="AB5">
+        <v>0.07486962988457473</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1208651922545404</v>
+      </c>
+      <c r="AD5">
+        <v>1819.2</v>
+      </c>
+      <c r="AE5">
+        <v>40.11634241760427</v>
+      </c>
+      <c r="AF5">
+        <v>1859.316342417604</v>
+      </c>
+      <c r="AG5">
+        <v>1210.616342417604</v>
+      </c>
+      <c r="AH5">
+        <v>0.677021912479621</v>
+      </c>
+      <c r="AI5">
+        <v>0.2678892263579511</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5771390687308959</v>
+      </c>
+      <c r="AK5">
+        <v>0.1924082070602416</v>
+      </c>
+      <c r="AL5">
+        <v>107.5</v>
+      </c>
+      <c r="AM5">
+        <v>61.2</v>
+      </c>
+      <c r="AN5">
+        <v>9.80700808625337</v>
+      </c>
+      <c r="AO5">
+        <v>-2.571162790697674</v>
+      </c>
+      <c r="AP5">
+        <v>6.526233651846924</v>
+      </c>
+      <c r="AQ5">
+        <v>-4.516339869281045</v>
       </c>
     </row>
   </sheetData>
